--- a/demoForm.xlsx
+++ b/demoForm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPPA\CMKL\Animation_Project\Summer\Experiment_Workflows\Testing1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC34BB6D-CD8A-46D9-92AC-1031000680ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D50DD22-4606-496A-A948-823DA82B3890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1464" yWindow="1464" windowWidth="12960" windowHeight="7824" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -772,7 +772,13 @@
       <c r="F2" s="2"/>
       <c r="G2" s="3"/>
       <c r="H2" s="2"/>
+      <c r="I2">
+        <v>1.5</v>
+      </c>
       <c r="J2" s="2"/>
+      <c r="K2">
+        <v>1</v>
+      </c>
       <c r="O2" s="4"/>
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
@@ -806,7 +812,7 @@
         <v>1.5</v>
       </c>
       <c r="K3">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -829,7 +835,7 @@
         <v>1.5</v>
       </c>
       <c r="K4">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
@@ -852,7 +858,7 @@
         <v>1.5</v>
       </c>
       <c r="K5">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/demoForm.xlsx
+++ b/demoForm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPPA\CMKL\Animation_Project\Summer\Experiment_Workflows\Testing1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\psychopyexperiments\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC34BB6D-CD8A-46D9-92AC-1031000680ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CCDBE8-6633-4174-A0CF-22BACED3EAC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1464" yWindow="1464" windowWidth="12960" windowHeight="7824" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -249,7 +249,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
   <si>
     <t>index</t>
   </si>
@@ -293,9 +293,6 @@
     <t>What is your age?</t>
   </si>
   <si>
-    <t>free text</t>
-  </si>
-  <si>
     <t>What is your gender?</t>
   </si>
   <si>
@@ -318,6 +315,12 @@
   </si>
   <si>
     <t>A1 - Beginner, A2 - Elementary, B1 - Intermediate, B2 - Upper-intermediate, C1 - Advanced, C2 - Proficient</t>
+  </si>
+  <si>
+    <t>horiz</t>
+  </si>
+  <si>
+    <t>18, 19, 20, 21, 22, 23, 24, 25</t>
   </si>
 </sst>
 </file>
@@ -691,19 +694,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z5"/>
-  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="12.69921875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.80859375" customWidth="1"/>
-    <col min="2" max="2" width="31.140625" customWidth="1"/>
-    <col min="3" max="3" width="13.6640625" customWidth="1"/>
+    <col min="1" max="1" width="5.796875" customWidth="1"/>
+    <col min="2" max="2" width="31.09765625" customWidth="1"/>
+    <col min="3" max="3" width="13.69921875" customWidth="1"/>
     <col min="4" max="4" width="84" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="22.47265625" customWidth="1"/>
-    <col min="7" max="7" width="9.33203125" customWidth="1"/>
-    <col min="8" max="13" width="13.6640625" customWidth="1"/>
-    <col min="14" max="26" width="7.6640625" customWidth="1"/>
+    <col min="5" max="6" width="22.5" customWidth="1"/>
+    <col min="7" max="7" width="9.296875" customWidth="1"/>
+    <col min="8" max="13" width="13.69921875" customWidth="1"/>
+    <col min="14" max="26" width="7.69921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -757,7 +760,7 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -765,14 +768,24 @@
         <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="3"/>
+        <v>15</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>23</v>
+      </c>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="3"/>
+      <c r="G2" s="3" t="s">
+        <v>22</v>
+      </c>
       <c r="H2" s="2"/>
+      <c r="I2">
+        <v>0.5</v>
+      </c>
       <c r="J2" s="2"/>
+      <c r="K2">
+        <v>1</v>
+      </c>
       <c r="O2" s="4"/>
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
@@ -786,73 +799,73 @@
       <c r="Y2" s="5"/>
       <c r="Z2" s="5"/>
     </row>
-    <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="G3" t="s">
         <v>17</v>
       </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
       <c r="I3">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="K3">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I4">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="K4">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" t="s">
         <v>21</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I5">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="K5">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/demoForm.xlsx
+++ b/demoForm.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Documents\psychopyexperiments\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPPA\CMKL\Animation_Project\Summer\Experiment_Workflows\Testing1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27CCDBE8-6633-4174-A0CF-22BACED3EAC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EC16E0-9962-4C8D-94B0-DD451EFEF2D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1464" yWindow="1464" windowWidth="12960" windowHeight="7824" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -249,7 +249,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
   <si>
     <t>index</t>
   </si>
@@ -317,10 +317,7 @@
     <t>A1 - Beginner, A2 - Elementary, B1 - Intermediate, B2 - Upper-intermediate, C1 - Advanced, C2 - Proficient</t>
   </si>
   <si>
-    <t>horiz</t>
-  </si>
-  <si>
-    <t>18, 19, 20, 21, 22, 23, 24, 25</t>
+    <t>18 years, 19 years, 20 years, 21 years, 22 years, 23 years, 24 years, 25 years</t>
   </si>
 </sst>
 </file>
@@ -359,7 +356,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -374,20 +371,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF66666E"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -395,94 +383,11 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="7">
-    <dxf>
-      <font>
-        <color rgb="FFACACB0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F2F2"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFACACB0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F2F2"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFACACB0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F2F2"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFACACB0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F2F2"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFACACB0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F2F2"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFACACB0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F2F2"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFACACB0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF2F2F2"/>
-          <bgColor rgb="FFF2F2F2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -694,19 +599,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Z5"/>
-  <sheetFormatPr defaultColWidth="12.69921875" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="5.796875" customWidth="1"/>
-    <col min="2" max="2" width="31.09765625" customWidth="1"/>
-    <col min="3" max="3" width="13.69921875" customWidth="1"/>
-    <col min="4" max="4" width="84" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="22.5" customWidth="1"/>
-    <col min="7" max="7" width="9.296875" customWidth="1"/>
-    <col min="8" max="13" width="13.69921875" customWidth="1"/>
-    <col min="14" max="26" width="7.69921875" customWidth="1"/>
+    <col min="1" max="1" width="5.80859375" customWidth="1"/>
+    <col min="2" max="2" width="31.09375" customWidth="1"/>
+    <col min="3" max="3" width="13.7109375" customWidth="1"/>
+    <col min="4" max="4" width="95" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="22.47265625" customWidth="1"/>
+    <col min="7" max="7" width="9.28515625" customWidth="1"/>
+    <col min="8" max="13" width="13.7109375" customWidth="1"/>
+    <col min="14" max="26" width="7.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -760,46 +665,30 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
     </row>
-    <row r="2" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2">
+    <row r="2" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="3" t="s">
+      <c r="D2" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="2"/>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
       <c r="I2">
-        <v>0.5</v>
-      </c>
-      <c r="J2" s="2"/>
+        <v>0.8</v>
+      </c>
       <c r="K2">
         <v>1</v>
       </c>
-      <c r="O2" s="4"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
     </row>
-    <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A3">
         <v>2</v>
       </c>
@@ -822,7 +711,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4">
         <v>3</v>
       </c>
@@ -845,7 +734,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5">
         <v>4</v>
       </c>
@@ -869,43 +758,9 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D2">
-    <cfRule type="expression" dxfId="6" priority="6">
-      <formula>AND(OR($C2="rating", $C2="slider", $C2="choice"), LEN($F2))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:G2 J2 L2">
-    <cfRule type="expression" dxfId="5" priority="1">
-      <formula>$C2="heading"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>$C2="description"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:G2 L2">
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>$C2="free text"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F2">
-    <cfRule type="expression" dxfId="2" priority="7">
-      <formula>AND(OR($C2="rating", $C2="slider", $C2="choice"), LEN($D2), LEN($F2)=0)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L2">
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>$C2="rating"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="5">
-      <formula>$C2="choice"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="C2:C5" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" sqref="C3:C5" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"heading,description,rating,slider,free text,choice"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2" xr:uid="{00000000-0002-0000-0000-000002000000}">
-      <formula1>"vert,horiz"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
